--- a/api/alembic/seeds/SpokenLanguageDirectoryMarch21_2023_CIS.xlsx
+++ b/api/alembic/seeds/SpokenLanguageDirectoryMarch21_2023_CIS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,41 @@
           <t>CONTRACT</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Demo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Interpreter</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/api/alembic/seeds/SpokenLanguageDirectoryMarch21_2023_CIS.xlsx
+++ b/api/alembic/seeds/SpokenLanguageDirectoryMarch21_2023_CIS.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>SPKL4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,19 +524,71 @@
           <t>Interpreter</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>220 W Broadway</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>92101</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>619-555-0100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>619-555-0101</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>619-555-0102</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>demo@example.com</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>S-0001</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>G-0001</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
